--- a/ig/ch-epl/StructureDefinition-ch-smc-loc-identifier.xlsx
+++ b/ig/ch-epl/StructureDefinition-ch-smc-loc-identifier.xlsx
@@ -30,19 +30,19 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>LOCIdentifier</t>
+    <t>SMCLOCIdentifier</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>LOC Identifier</t>
+    <t>SMC Identifier</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-11T12:35:50+00:00</t>
+    <t>2026-04-07T14:09:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Identifier holding a number for LocID (Location Identifier of the European Medicines Agency - Organisation Management System OMS)</t>
+    <t>Identifier holding a number for Organisations registered at Swissmedic</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -420,7 +420,7 @@
 </t>
   </si>
   <si>
-    <t>LocID</t>
+    <t>SMCLocID</t>
   </si>
   <si>
     <t>Establishes the namespace for the value - that is, an absolute URL that describes a set values that are unique.</t>
@@ -432,7 +432,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.276.0.76</t>
+    <t>https://www.swissmedic.ch/fhir/identifier/locations</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
